--- a/data/NED (v.0.1).xlsx
+++ b/data/NED (v.0.1).xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N128"/>
+  <dimension ref="A1:N122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -405,7 +405,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>reelec_nat_exe</t>
+          <t>consecutive_reelection_nat_exe</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -923,11 +923,11 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1141,17 +1141,17 @@
         </is>
       </c>
       <c r="F13" s="2">
-        <v>32697</v>
+        <v>34888</v>
       </c>
       <c r="G13" s="2">
-        <v>34888</v>
+        <v>36504</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>4.423497267759563</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1233,11 +1233,11 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N14">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="C15">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1295,11 +1295,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N15">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1357,11 +1357,11 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -1438,11 +1438,11 @@
         </is>
       </c>
       <c r="C18">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CARLOS SAÚL MENEM</t>
+          <t>FERNANDO DE LA RÚA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1451,17 +1451,17 @@
         </is>
       </c>
       <c r="F18" s="2">
-        <v>34888</v>
+        <v>36504</v>
       </c>
       <c r="G18" s="2">
-        <v>36504</v>
+        <v>37246</v>
       </c>
       <c r="H18">
-        <v>4.423497267759563</v>
+        <v>2.03013698630137</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1471,21 +1471,21 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>PARTIDO JUSTICIALISTA</t>
+          <t>ALIANZA PARA EL TRABAJO, LA JUSTICIA Y LA EDUCACIÓN (UCR-FREPASO)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N18">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1500,11 +1500,11 @@
         </is>
       </c>
       <c r="C19">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CARLOS SAÚL MENEM</t>
+          <t>FERNANDO DE LA RÚA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1513,17 +1513,17 @@
         </is>
       </c>
       <c r="F19" s="2">
-        <v>34888</v>
+        <v>36504</v>
       </c>
       <c r="G19" s="2">
-        <v>36504</v>
+        <v>37246</v>
       </c>
       <c r="H19">
-        <v>4.423497267759563</v>
+        <v>2.03013698630137</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>PARTIDO JUSTICIALISTA</t>
+          <t>ALIANZA PARA EL TRABAJO, LA JUSTICIA Y LA EDUCACIÓN (UCR-FREPASO)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1605,11 +1605,11 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1624,11 +1624,11 @@
         </is>
       </c>
       <c r="C21">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FERNANDO DE LA RÚA</t>
+          <t>EDUARDO ALBERTO DUHALDE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1637,13 +1637,13 @@
         </is>
       </c>
       <c r="F21" s="2">
-        <v>36504</v>
+        <v>37258</v>
       </c>
       <c r="G21" s="2">
-        <v>37246</v>
+        <v>37766</v>
       </c>
       <c r="H21">
-        <v>2.03013698630137</v>
+        <v>1.391780821917808</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1657,21 +1657,21 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>ALIANZA PARA EL TRABAJO, LA JUSTICIA Y LA EDUCACIÓN (UCR-FREPASO)</t>
+          <t>PARTIDO JUSTICIALISTA</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1686,11 +1686,11 @@
         </is>
       </c>
       <c r="C22">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FERNANDO DE LA RÚA</t>
+          <t>NÉSTOR CARLOS KIRCHNER</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1699,13 +1699,13 @@
         </is>
       </c>
       <c r="F22" s="2">
-        <v>36504</v>
+        <v>37766</v>
       </c>
       <c r="G22" s="2">
-        <v>37246</v>
+        <v>39426</v>
       </c>
       <c r="H22">
-        <v>2.03013698630137</v>
+        <v>4.543715846994536</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>ALIANZA PARA EL TRABAJO, LA JUSTICIA Y LA EDUCACIÓN (UCR-FREPASO)</t>
+          <t>PARTIDO JUSTICIALISTA</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1748,11 +1748,11 @@
         </is>
       </c>
       <c r="C23">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FERNANDO DE LA RÚA</t>
+          <t>NÉSTOR CARLOS KIRCHNER</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="F23" s="2">
-        <v>36504</v>
+        <v>37766</v>
       </c>
       <c r="G23" s="2">
-        <v>37246</v>
+        <v>39426</v>
       </c>
       <c r="H23">
-        <v>2.03013698630137</v>
+        <v>4.543715846994536</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1776,17 +1776,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>ALIANZA PARA EL TRABAJO, LA JUSTICIA Y LA EDUCACIÓN (UCR-FREPASO)</t>
+          <t>PARTIDO JUSTICIALISTA</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1810,11 +1810,11 @@
         </is>
       </c>
       <c r="C24">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EDUARDO ALBERTO DUHALDE</t>
+          <t>NÉSTOR CARLOS KIRCHNER</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="F24" s="2">
-        <v>37258</v>
+        <v>37766</v>
       </c>
       <c r="G24" s="2">
-        <v>37766</v>
+        <v>39426</v>
       </c>
       <c r="H24">
-        <v>1.391780821917808</v>
+        <v>4.543715846994536</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1872,7 +1872,7 @@
         </is>
       </c>
       <c r="C25">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1915,11 +1915,11 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N25">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1934,26 +1934,26 @@
         </is>
       </c>
       <c r="C26">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NÉSTOR CARLOS KIRCHNER</t>
+          <t>CRISTINA FERNÁNDEZ DE KIRCHNER</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F26" s="2">
-        <v>37766</v>
+        <v>39426</v>
       </c>
       <c r="G26" s="2">
-        <v>39426</v>
+        <v>40887</v>
       </c>
       <c r="H26">
-        <v>4.543715846994536</v>
+        <v>4</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1996,26 +1996,26 @@
         </is>
       </c>
       <c r="C27">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NÉSTOR CARLOS KIRCHNER</t>
+          <t>CRISTINA FERNÁNDEZ DE KIRCHNER</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F27" s="2">
-        <v>37766</v>
+        <v>39426</v>
       </c>
       <c r="G27" s="2">
-        <v>39426</v>
+        <v>40887</v>
       </c>
       <c r="H27">
-        <v>4.543715846994536</v>
+        <v>4</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2058,26 +2058,26 @@
         </is>
       </c>
       <c r="C28">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NÉSTOR CARLOS KIRCHNER</t>
+          <t>CRISTINA FERNÁNDEZ DE KIRCHNER</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F28" s="2">
-        <v>37766</v>
+        <v>39426</v>
       </c>
       <c r="G28" s="2">
-        <v>39426</v>
+        <v>40887</v>
       </c>
       <c r="H28">
-        <v>4.543715846994536</v>
+        <v>4</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2120,26 +2120,26 @@
         </is>
       </c>
       <c r="C29">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NÉSTOR CARLOS KIRCHNER</t>
+          <t>CRISTINA FERNÁNDEZ DE KIRCHNER</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F29" s="2">
-        <v>37766</v>
+        <v>39426</v>
       </c>
       <c r="G29" s="2">
-        <v>39426</v>
+        <v>40887</v>
       </c>
       <c r="H29">
-        <v>4.543715846994536</v>
+        <v>4</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2195,17 +2195,17 @@
         </is>
       </c>
       <c r="F30" s="2">
-        <v>39426</v>
+        <v>40887</v>
       </c>
       <c r="G30" s="2">
-        <v>40887</v>
+        <v>42348</v>
       </c>
       <c r="H30">
         <v>4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2257,17 +2257,17 @@
         </is>
       </c>
       <c r="F31" s="2">
-        <v>39426</v>
+        <v>40887</v>
       </c>
       <c r="G31" s="2">
-        <v>40887</v>
+        <v>42348</v>
       </c>
       <c r="H31">
         <v>4</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2319,17 +2319,17 @@
         </is>
       </c>
       <c r="F32" s="2">
-        <v>39426</v>
+        <v>40887</v>
       </c>
       <c r="G32" s="2">
-        <v>40887</v>
+        <v>42348</v>
       </c>
       <c r="H32">
         <v>4</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2381,17 +2381,17 @@
         </is>
       </c>
       <c r="F33" s="2">
-        <v>39426</v>
+        <v>40887</v>
       </c>
       <c r="G33" s="2">
-        <v>40887</v>
+        <v>42348</v>
       </c>
       <c r="H33">
         <v>4</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -2430,30 +2430,30 @@
         </is>
       </c>
       <c r="C34">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CRISTINA FERNÁNDEZ DE KIRCHNER</t>
+          <t>MAURICIO MACRI</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F34" s="2">
-        <v>40887</v>
+        <v>42348</v>
       </c>
       <c r="G34" s="2">
-        <v>42348</v>
+        <v>43809</v>
       </c>
       <c r="H34">
         <v>4</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>PARTIDO JUSTICIALISTA</t>
+          <t>PROPUESTA REPUBLICANA</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2492,30 +2492,30 @@
         </is>
       </c>
       <c r="C35">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CRISTINA FERNÁNDEZ DE KIRCHNER</t>
+          <t>MAURICIO MACRI</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F35" s="2">
-        <v>40887</v>
+        <v>42348</v>
       </c>
       <c r="G35" s="2">
-        <v>42348</v>
+        <v>43809</v>
       </c>
       <c r="H35">
         <v>4</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2525,21 +2525,21 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>PARTIDO JUSTICIALISTA</t>
+          <t>PROPUESTA REPUBLICANA</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N35">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2554,30 +2554,30 @@
         </is>
       </c>
       <c r="C36">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CRISTINA FERNÁNDEZ DE KIRCHNER</t>
+          <t>MAURICIO MACRI</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F36" s="2">
-        <v>40887</v>
+        <v>42348</v>
       </c>
       <c r="G36" s="2">
-        <v>42348</v>
+        <v>43809</v>
       </c>
       <c r="H36">
         <v>4</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>PARTIDO JUSTICIALISTA</t>
+          <t>PROPUESTA REPUBLICANA</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2616,30 +2616,30 @@
         </is>
       </c>
       <c r="C37">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CRISTINA FERNÁNDEZ DE KIRCHNER</t>
+          <t>MAURICIO MACRI</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" s="2">
-        <v>40887</v>
+        <v>42348</v>
       </c>
       <c r="G37" s="2">
-        <v>42348</v>
+        <v>43809</v>
       </c>
       <c r="H37">
         <v>4</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>PARTIDO JUSTICIALISTA</t>
+          <t>PROPUESTA REPUBLICANA</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2678,30 +2678,30 @@
         </is>
       </c>
       <c r="C38">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CRISTINA FERNÁNDEZ DE KIRCHNER</t>
+          <t>ALBERTO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" s="2">
-        <v>40887</v>
+        <v>43809</v>
       </c>
       <c r="G38" s="2">
-        <v>42348</v>
+        <v>45270</v>
       </c>
       <c r="H38">
         <v>4</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2721,11 +2721,11 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N38">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2740,11 +2740,11 @@
         </is>
       </c>
       <c r="C39">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MAURICIO MACRI</t>
+          <t>ALBERTO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="F39" s="2">
-        <v>42348</v>
+        <v>43809</v>
       </c>
       <c r="G39" s="2">
-        <v>43809</v>
+        <v>45270</v>
       </c>
       <c r="H39">
         <v>4</v>
@@ -2773,21 +2773,21 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>PROPUESTA REPUBLICANA</t>
+          <t>PARTIDO JUSTICIALISTA</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N39">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2802,11 +2802,11 @@
         </is>
       </c>
       <c r="C40">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MAURICIO MACRI</t>
+          <t>ALBERTO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="F40" s="2">
-        <v>42348</v>
+        <v>43809</v>
       </c>
       <c r="G40" s="2">
-        <v>43809</v>
+        <v>45270</v>
       </c>
       <c r="H40">
         <v>4</v>
@@ -2835,21 +2835,21 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>PROPUESTA REPUBLICANA</t>
+          <t>PARTIDO JUSTICIALISTA</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N40">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2864,11 +2864,11 @@
         </is>
       </c>
       <c r="C41">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MAURICIO MACRI</t>
+          <t>ALBERTO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F41" s="2">
-        <v>42348</v>
+        <v>43809</v>
       </c>
       <c r="G41" s="2">
-        <v>43809</v>
+        <v>45270</v>
       </c>
       <c r="H41">
         <v>4</v>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>PROPUESTA REPUBLICANA</t>
+          <t>PARTIDO JUSTICIALISTA</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2926,11 +2926,11 @@
         </is>
       </c>
       <c r="C42">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MAURICIO MACRI</t>
+          <t>JAVIER GERARDO MILEI</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2939,13 +2939,7 @@
         </is>
       </c>
       <c r="F42" s="2">
-        <v>42348</v>
-      </c>
-      <c r="G42" s="2">
-        <v>43809</v>
-      </c>
-      <c r="H42">
-        <v>4</v>
+        <v>45270</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2959,21 +2953,21 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>PROPUESTA REPUBLICANA</t>
+          <t>LA LIBERTAD AVANZA</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N42">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2988,11 +2982,11 @@
         </is>
       </c>
       <c r="C43">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MAURICIO MACRI</t>
+          <t>JAVIER GERARDO MILEI</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3001,13 +2995,7 @@
         </is>
       </c>
       <c r="F43" s="2">
-        <v>42348</v>
-      </c>
-      <c r="G43" s="2">
-        <v>43809</v>
-      </c>
-      <c r="H43">
-        <v>4</v>
+        <v>45270</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3021,12 +3009,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>PROPUESTA REPUBLICANA</t>
+          <t>LA LIBERTAD AVANZA</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3035,26 +3023,26 @@
         </is>
       </c>
       <c r="N43">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ARGENTINA</t>
+          <t>BRAZIL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>032</t>
+          <t>076</t>
         </is>
       </c>
       <c r="C44">
-        <v>2019</v>
+        <v>1986</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ALBERTO FERNÁNDEZ</t>
+          <t>JOSÉ SARNEY COSTA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3063,13 +3051,13 @@
         </is>
       </c>
       <c r="F44" s="2">
-        <v>43809</v>
+        <v>31121</v>
       </c>
       <c r="G44" s="2">
-        <v>45270</v>
+        <v>32947</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3083,40 +3071,40 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>PARTIDO JUSTICIALISTA</t>
+          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ARGENTINA</t>
+          <t>BRAZIL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>032</t>
+          <t>076</t>
         </is>
       </c>
       <c r="C45">
-        <v>2020</v>
+        <v>1987</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ALBERTO FERNÁNDEZ</t>
+          <t>JOSÉ SARNEY COSTA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3125,13 +3113,13 @@
         </is>
       </c>
       <c r="F45" s="2">
-        <v>43809</v>
+        <v>31121</v>
       </c>
       <c r="G45" s="2">
-        <v>45270</v>
+        <v>32947</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3145,12 +3133,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>PARTIDO JUSTICIALISTA</t>
+          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3159,26 +3147,26 @@
         </is>
       </c>
       <c r="N45">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ARGENTINA</t>
+          <t>BRAZIL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>032</t>
+          <t>076</t>
         </is>
       </c>
       <c r="C46">
-        <v>2021</v>
+        <v>1988</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ALBERTO FERNÁNDEZ</t>
+          <t>JOSÉ SARNEY COSTA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3187,13 +3175,13 @@
         </is>
       </c>
       <c r="F46" s="2">
-        <v>43809</v>
+        <v>31121</v>
       </c>
       <c r="G46" s="2">
-        <v>45270</v>
+        <v>32947</v>
       </c>
       <c r="H46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3207,12 +3195,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>PARTIDO JUSTICIALISTA</t>
+          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3221,26 +3209,26 @@
         </is>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ARGENTINA</t>
+          <t>BRAZIL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>032</t>
+          <t>076</t>
         </is>
       </c>
       <c r="C47">
-        <v>2022</v>
+        <v>1989</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ALBERTO FERNÁNDEZ</t>
+          <t>JOSÉ SARNEY COSTA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3249,13 +3237,13 @@
         </is>
       </c>
       <c r="F47" s="2">
-        <v>43809</v>
+        <v>31121</v>
       </c>
       <c r="G47" s="2">
-        <v>45270</v>
+        <v>32947</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3269,40 +3257,40 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>PARTIDO JUSTICIALISTA</t>
+          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ARGENTINA</t>
+          <t>BRAZIL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>032</t>
+          <t>076</t>
         </is>
       </c>
       <c r="C48">
-        <v>2023</v>
+        <v>1990</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JAVIER GERARDO MILEI</t>
+          <t>FERNANDO AFFONSO COLLOR DE MELLO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3311,7 +3299,13 @@
         </is>
       </c>
       <c r="F48" s="2">
-        <v>45270</v>
+        <v>32947</v>
+      </c>
+      <c r="G48" s="2">
+        <v>33967</v>
+      </c>
+      <c r="H48">
+        <v>2.791780821917808</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3325,7 +3319,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LA LIBERTAD AVANZA</t>
+          <t>PARTIDO DE LA RECONSTRUCCIÓN NACIONAL / PARTIDO LABORISTA CRISTIANO</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3335,30 +3329,30 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ARGENTINA</t>
+          <t>BRAZIL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>032</t>
+          <t>076</t>
         </is>
       </c>
       <c r="C49">
-        <v>2024</v>
+        <v>1991</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JAVIER GERARDO MILEI</t>
+          <t>FERNANDO AFFONSO COLLOR DE MELLO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3367,7 +3361,13 @@
         </is>
       </c>
       <c r="F49" s="2">
-        <v>45270</v>
+        <v>32947</v>
+      </c>
+      <c r="G49" s="2">
+        <v>33967</v>
+      </c>
+      <c r="H49">
+        <v>2.791780821917808</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3376,12 +3376,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LA LIBERTAD AVANZA</t>
+          <t>PARTIDO DE LA RECONSTRUCCIÓN NACIONAL / PARTIDO LABORISTA CRISTIANO</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3410,11 +3410,11 @@
         </is>
       </c>
       <c r="C50">
-        <v>1986</v>
+        <v>1992</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JOSÉ SARNEY COSTA</t>
+          <t>ITAMAR AUGUSTO CAUTIERO FRANCO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3423,13 +3423,13 @@
         </is>
       </c>
       <c r="F50" s="2">
-        <v>31121</v>
+        <v>33967</v>
       </c>
       <c r="G50" s="2">
-        <v>32947</v>
+        <v>34699</v>
       </c>
       <c r="H50">
-        <v>5</v>
+        <v>2.005479452054795</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3443,12 +3443,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
+          <t>INDEPENDENT</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3472,11 +3472,11 @@
         </is>
       </c>
       <c r="C51">
-        <v>1987</v>
+        <v>1993</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JOSÉ SARNEY COSTA</t>
+          <t>ITAMAR AUGUSTO CAUTIERO FRANCO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3485,13 +3485,13 @@
         </is>
       </c>
       <c r="F51" s="2">
-        <v>31121</v>
+        <v>33967</v>
       </c>
       <c r="G51" s="2">
-        <v>32947</v>
+        <v>34699</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>2.005479452054795</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
+          <t>INDEPENDENT</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="C52">
-        <v>1988</v>
+        <v>1994</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JOSÉ SARNEY COSTA</t>
+          <t>ITAMAR AUGUSTO CAUTIERO FRANCO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3547,13 +3547,13 @@
         </is>
       </c>
       <c r="F52" s="2">
-        <v>31121</v>
+        <v>33967</v>
       </c>
       <c r="G52" s="2">
-        <v>32947</v>
+        <v>34699</v>
       </c>
       <c r="H52">
-        <v>5</v>
+        <v>2.005479452054795</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3567,21 +3567,21 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
+          <t>INDEPENDENT</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N52">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3596,11 +3596,11 @@
         </is>
       </c>
       <c r="C53">
-        <v>1989</v>
+        <v>1995</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JOSÉ SARNEY COSTA</t>
+          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3609,13 +3609,13 @@
         </is>
       </c>
       <c r="F53" s="2">
-        <v>31121</v>
+        <v>34700</v>
       </c>
       <c r="G53" s="2">
-        <v>32947</v>
+        <v>36160</v>
       </c>
       <c r="H53">
-        <v>5</v>
+        <v>3.997260273972603</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
+          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3639,11 +3639,11 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3658,11 +3658,11 @@
         </is>
       </c>
       <c r="C54">
-        <v>1990</v>
+        <v>1996</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FERNANDO AFFONSO COLLOR DE MELLO</t>
+          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="F54" s="2">
-        <v>32947</v>
+        <v>34700</v>
       </c>
       <c r="G54" s="2">
-        <v>33967</v>
+        <v>36160</v>
       </c>
       <c r="H54">
-        <v>2.791780821917808</v>
+        <v>3.997260273972603</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>PARTIDO DE LA RECONSTRUCCIÓN NACIONAL / PARTIDO LABORISTA CRISTIANO</t>
+          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3720,11 +3720,11 @@
         </is>
       </c>
       <c r="C55">
-        <v>1991</v>
+        <v>1997</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FERNANDO AFFONSO COLLOR DE MELLO</t>
+          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3733,13 +3733,13 @@
         </is>
       </c>
       <c r="F55" s="2">
-        <v>32947</v>
+        <v>34700</v>
       </c>
       <c r="G55" s="2">
-        <v>33967</v>
+        <v>36160</v>
       </c>
       <c r="H55">
-        <v>2.791780821917808</v>
+        <v>3.997260273972603</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3748,17 +3748,17 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>PARTIDO DE LA RECONSTRUCCIÓN NACIONAL / PARTIDO LABORISTA CRISTIANO</t>
+          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3782,11 +3782,11 @@
         </is>
       </c>
       <c r="C56">
-        <v>1992</v>
+        <v>1998</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ITAMAR AUGUSTO CAUTIERO FRANCO</t>
+          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3795,13 +3795,13 @@
         </is>
       </c>
       <c r="F56" s="2">
-        <v>33967</v>
+        <v>34700</v>
       </c>
       <c r="G56" s="2">
-        <v>34699</v>
+        <v>36160</v>
       </c>
       <c r="H56">
-        <v>2.005479452054795</v>
+        <v>3.997260273972603</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3815,21 +3815,21 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>INDEPENDENT</t>
+          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N56">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3844,11 +3844,11 @@
         </is>
       </c>
       <c r="C57">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ITAMAR AUGUSTO CAUTIERO FRANCO</t>
+          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3857,17 +3857,17 @@
         </is>
       </c>
       <c r="F57" s="2">
-        <v>33967</v>
+        <v>36161</v>
       </c>
       <c r="G57" s="2">
-        <v>34699</v>
+        <v>37621</v>
       </c>
       <c r="H57">
-        <v>2.005479452054795</v>
+        <v>3.997260273972603</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>INDEPENDENT</t>
+          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3906,11 +3906,11 @@
         </is>
       </c>
       <c r="C58">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ITAMAR AUGUSTO CAUTIERO FRANCO</t>
+          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3919,17 +3919,17 @@
         </is>
       </c>
       <c r="F58" s="2">
-        <v>33967</v>
+        <v>36161</v>
       </c>
       <c r="G58" s="2">
-        <v>34699</v>
+        <v>37621</v>
       </c>
       <c r="H58">
-        <v>2.005479452054795</v>
+        <v>3.997260273972603</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3939,21 +3939,21 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>INDEPENDENT</t>
+          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N58">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="C59">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -3981,17 +3981,17 @@
         </is>
       </c>
       <c r="F59" s="2">
-        <v>34700</v>
+        <v>36161</v>
       </c>
       <c r="G59" s="2">
-        <v>36160</v>
+        <v>37621</v>
       </c>
       <c r="H59">
         <v>3.997260273972603</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
@@ -4030,7 +4030,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>1996</v>
+        <v>2002</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4043,17 +4043,17 @@
         </is>
       </c>
       <c r="F60" s="2">
-        <v>34700</v>
+        <v>36161</v>
       </c>
       <c r="G60" s="2">
-        <v>36160</v>
+        <v>37621</v>
       </c>
       <c r="H60">
         <v>3.997260273972603</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4073,11 +4073,11 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N60">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61">
@@ -4092,11 +4092,11 @@
         </is>
       </c>
       <c r="C61">
-        <v>1997</v>
+        <v>2003</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
+          <t>LUIZ INÁCIO LULA DA SILVA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="F61" s="2">
-        <v>34700</v>
+        <v>37622</v>
       </c>
       <c r="G61" s="2">
-        <v>36160</v>
+        <v>39082</v>
       </c>
       <c r="H61">
         <v>3.997260273972603</v>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
+          <t>PARTIDO DE LOS TRABAJADORES</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -4154,11 +4154,11 @@
         </is>
       </c>
       <c r="C62">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
+          <t>LUIZ INÁCIO LULA DA SILVA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="F62" s="2">
-        <v>34700</v>
+        <v>37622</v>
       </c>
       <c r="G62" s="2">
-        <v>36160</v>
+        <v>39082</v>
       </c>
       <c r="H62">
         <v>3.997260273972603</v>
@@ -4187,21 +4187,21 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
+          <t>PARTIDO DE LOS TRABAJADORES</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4216,11 +4216,11 @@
         </is>
       </c>
       <c r="C63">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
+          <t>LUIZ INÁCIO LULA DA SILVA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4229,17 +4229,17 @@
         </is>
       </c>
       <c r="F63" s="2">
-        <v>36161</v>
+        <v>37622</v>
       </c>
       <c r="G63" s="2">
-        <v>37621</v>
+        <v>39082</v>
       </c>
       <c r="H63">
         <v>3.997260273972603</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
+          <t>PARTIDO DE LOS TRABAJADORES</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4278,11 +4278,11 @@
         </is>
       </c>
       <c r="C64">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
+          <t>LUIZ INÁCIO LULA DA SILVA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4291,17 +4291,17 @@
         </is>
       </c>
       <c r="F64" s="2">
-        <v>36161</v>
+        <v>37622</v>
       </c>
       <c r="G64" s="2">
-        <v>37621</v>
+        <v>39082</v>
       </c>
       <c r="H64">
         <v>3.997260273972603</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4311,21 +4311,21 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
+          <t>PARTIDO DE LOS TRABAJADORES</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N64">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4340,11 +4340,11 @@
         </is>
       </c>
       <c r="C65">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
+          <t>LUIZ INÁCIO LULA DA SILVA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="F65" s="2">
-        <v>36161</v>
+        <v>39083</v>
       </c>
       <c r="G65" s="2">
-        <v>37621</v>
+        <v>40543</v>
       </c>
       <c r="H65">
         <v>3.997260273972603</v>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
+          <t>PARTIDO DE LOS TRABAJADORES</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4402,11 +4402,11 @@
         </is>
       </c>
       <c r="C66">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FERNANDO HENRIQUE SILVA CARDOSO</t>
+          <t>LUIZ INÁCIO LULA DA SILVA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="F66" s="2">
-        <v>36161</v>
+        <v>39083</v>
       </c>
       <c r="G66" s="2">
-        <v>37621</v>
+        <v>40543</v>
       </c>
       <c r="H66">
         <v>3.997260273972603</v>
@@ -4435,21 +4435,21 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>PARTIDO DE LA SOCIAL DEMOCRACIA BRASILEÑA</t>
+          <t>PARTIDO DE LOS TRABAJADORES</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N66">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="C67">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -4477,17 +4477,17 @@
         </is>
       </c>
       <c r="F67" s="2">
-        <v>37622</v>
+        <v>39083</v>
       </c>
       <c r="G67" s="2">
-        <v>39082</v>
+        <v>40543</v>
       </c>
       <c r="H67">
         <v>3.997260273972603</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="C68">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -4539,17 +4539,17 @@
         </is>
       </c>
       <c r="F68" s="2">
-        <v>37622</v>
+        <v>39083</v>
       </c>
       <c r="G68" s="2">
-        <v>39082</v>
+        <v>40543</v>
       </c>
       <c r="H68">
         <v>3.997260273972603</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4569,11 +4569,11 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -4588,23 +4588,23 @@
         </is>
       </c>
       <c r="C69">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LUIZ INÁCIO LULA DA SILVA</t>
+          <t>DILMA VANA ROUSSEFF</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F69" s="2">
-        <v>37622</v>
+        <v>40544</v>
       </c>
       <c r="G69" s="2">
-        <v>39082</v>
+        <v>42004</v>
       </c>
       <c r="H69">
         <v>3.997260273972603</v>
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4650,23 +4650,23 @@
         </is>
       </c>
       <c r="C70">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LUIZ INÁCIO LULA DA SILVA</t>
+          <t>DILMA VANA ROUSSEFF</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F70" s="2">
-        <v>37622</v>
+        <v>40544</v>
       </c>
       <c r="G70" s="2">
-        <v>39082</v>
+        <v>42004</v>
       </c>
       <c r="H70">
         <v>3.997260273972603</v>
@@ -4693,11 +4693,11 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N70">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4712,30 +4712,30 @@
         </is>
       </c>
       <c r="C71">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LUIZ INÁCIO LULA DA SILVA</t>
+          <t>DILMA VANA ROUSSEFF</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F71" s="2">
-        <v>39083</v>
+        <v>40544</v>
       </c>
       <c r="G71" s="2">
-        <v>40543</v>
+        <v>42004</v>
       </c>
       <c r="H71">
         <v>3.997260273972603</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4774,30 +4774,30 @@
         </is>
       </c>
       <c r="C72">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LUIZ INÁCIO LULA DA SILVA</t>
+          <t>DILMA VANA ROUSSEFF</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F72" s="2">
-        <v>39083</v>
+        <v>40544</v>
       </c>
       <c r="G72" s="2">
-        <v>40543</v>
+        <v>42004</v>
       </c>
       <c r="H72">
         <v>3.997260273972603</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4817,11 +4817,11 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N72">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
@@ -4836,26 +4836,26 @@
         </is>
       </c>
       <c r="C73">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LUIZ INÁCIO LULA DA SILVA</t>
+          <t>DILMA VANA ROUSSEFF</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F73" s="2">
-        <v>39083</v>
+        <v>42005</v>
       </c>
       <c r="G73" s="2">
-        <v>40543</v>
+        <v>42613</v>
       </c>
       <c r="H73">
-        <v>3.997260273972603</v>
+        <v>1.663934426229508</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -4898,11 +4898,11 @@
         </is>
       </c>
       <c r="C74">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LUIZ INÁCIO LULA DA SILVA</t>
+          <t>MICHEL MIGUEL ELIAS TEMER LULIA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4911,17 +4911,17 @@
         </is>
       </c>
       <c r="F74" s="2">
-        <v>39083</v>
+        <v>42613</v>
       </c>
       <c r="G74" s="2">
-        <v>40543</v>
+        <v>43465</v>
       </c>
       <c r="H74">
-        <v>3.997260273972603</v>
+        <v>2.334246575342466</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4931,21 +4931,21 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>PARTIDO DE LOS TRABAJADORES</t>
+          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N74">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4960,26 +4960,26 @@
         </is>
       </c>
       <c r="C75">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DILMA VANA ROUSSEFF</t>
+          <t>MICHEL MIGUEL ELIAS TEMER LULIA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F75" s="2">
-        <v>40544</v>
+        <v>42613</v>
       </c>
       <c r="G75" s="2">
-        <v>42004</v>
+        <v>43465</v>
       </c>
       <c r="H75">
-        <v>3.997260273972603</v>
+        <v>2.334246575342466</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4993,12 +4993,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>PARTIDO DE LOS TRABAJADORES</t>
+          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5022,26 +5022,26 @@
         </is>
       </c>
       <c r="C76">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DILMA VANA ROUSSEFF</t>
+          <t>MICHEL MIGUEL ELIAS TEMER LULIA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F76" s="2">
-        <v>40544</v>
+        <v>42613</v>
       </c>
       <c r="G76" s="2">
-        <v>42004</v>
+        <v>43465</v>
       </c>
       <c r="H76">
-        <v>3.997260273972603</v>
+        <v>2.334246575342466</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -5055,17 +5055,17 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>PARTIDO DE LOS TRABAJADORES</t>
+          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N76">
@@ -5084,23 +5084,23 @@
         </is>
       </c>
       <c r="C77">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DILMA VANA ROUSSEFF</t>
+          <t>JAIR MESSIAS BOLSONARO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F77" s="2">
-        <v>40544</v>
+        <v>43466</v>
       </c>
       <c r="G77" s="2">
-        <v>42004</v>
+        <v>44926</v>
       </c>
       <c r="H77">
         <v>3.997260273972603</v>
@@ -5117,12 +5117,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>PARTIDO DE LOS TRABAJADORES</t>
+          <t>INDEPENDENT</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5146,23 +5146,23 @@
         </is>
       </c>
       <c r="C78">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DILMA VANA ROUSSEFF</t>
+          <t>JAIR MESSIAS BOLSONARO</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F78" s="2">
-        <v>40544</v>
+        <v>43466</v>
       </c>
       <c r="G78" s="2">
-        <v>42004</v>
+        <v>44926</v>
       </c>
       <c r="H78">
         <v>3.997260273972603</v>
@@ -5179,21 +5179,21 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>PARTIDO DE LOS TRABAJADORES</t>
+          <t>INDEPENDENT</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N78">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -5208,45 +5208,45 @@
         </is>
       </c>
       <c r="C79">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DILMA VANA ROUSSEFF</t>
+          <t>JAIR MESSIAS BOLSONARO</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F79" s="2">
-        <v>42005</v>
+        <v>43466</v>
       </c>
       <c r="G79" s="2">
-        <v>42613</v>
+        <v>44926</v>
       </c>
       <c r="H79">
-        <v>1.663934426229508</v>
+        <v>3.997260273972603</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>PARTIDO DE LOS TRABAJADORES</t>
+          <t>PARTIDO LIBERAL</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -5270,11 +5270,11 @@
         </is>
       </c>
       <c r="C80">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MICHEL MIGUEL ELIAS TEMER LULIA</t>
+          <t>JAIR MESSIAS BOLSONARO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5283,13 +5283,13 @@
         </is>
       </c>
       <c r="F80" s="2">
-        <v>42613</v>
+        <v>43466</v>
       </c>
       <c r="G80" s="2">
-        <v>43465</v>
+        <v>44926</v>
       </c>
       <c r="H80">
-        <v>2.334246575342466</v>
+        <v>3.997260273972603</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -5303,21 +5303,21 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
+          <t>PARTIDO LIBERAL</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N80">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -5332,11 +5332,11 @@
         </is>
       </c>
       <c r="C81">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MICHEL MIGUEL ELIAS TEMER LULIA</t>
+          <t>LUIZ INÁCIO LULA DA SILVA</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5345,13 +5345,7 @@
         </is>
       </c>
       <c r="F81" s="2">
-        <v>42613</v>
-      </c>
-      <c r="G81" s="2">
-        <v>43465</v>
-      </c>
-      <c r="H81">
-        <v>2.334246575342466</v>
+        <v>44927</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -5365,12 +5359,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
+          <t>PARTIDO DE LOS TRABAJADORES</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5379,7 +5373,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
@@ -5394,11 +5388,11 @@
         </is>
       </c>
       <c r="C82">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>MICHEL MIGUEL ELIAS TEMER LULIA</t>
+          <t>LUIZ INÁCIO LULA DA SILVA</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5407,13 +5401,7 @@
         </is>
       </c>
       <c r="F82" s="2">
-        <v>42613</v>
-      </c>
-      <c r="G82" s="2">
-        <v>43465</v>
-      </c>
-      <c r="H82">
-        <v>2.334246575342466</v>
+        <v>44927</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -5427,40 +5415,40 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>PARTIDO DEL MOVIMIENTO DEMOCRÁTICO BRASILEÑO (PMDB)</t>
+          <t>PARTIDO DE LOS TRABAJADORES</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N82">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>484</t>
         </is>
       </c>
       <c r="C83">
-        <v>2019</v>
+        <v>1985</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>JAIR MESSIAS BOLSONARO</t>
+          <t>MIGUEL DE LA MADRID HURTADO</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5469,13 +5457,13 @@
         </is>
       </c>
       <c r="F83" s="2">
-        <v>43466</v>
+        <v>30286</v>
       </c>
       <c r="G83" s="2">
-        <v>44926</v>
+        <v>32477</v>
       </c>
       <c r="H83">
-        <v>3.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5489,12 +5477,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>INDEPENDENT</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -5503,26 +5491,26 @@
         </is>
       </c>
       <c r="N83">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>484</t>
         </is>
       </c>
       <c r="C84">
-        <v>2020</v>
+        <v>1986</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>JAIR MESSIAS BOLSONARO</t>
+          <t>MIGUEL DE LA MADRID HURTADO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5531,13 +5519,13 @@
         </is>
       </c>
       <c r="F84" s="2">
-        <v>43466</v>
+        <v>30286</v>
       </c>
       <c r="G84" s="2">
-        <v>44926</v>
+        <v>32477</v>
       </c>
       <c r="H84">
-        <v>3.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5551,12 +5539,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>INDEPENDENT</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -5565,26 +5553,26 @@
         </is>
       </c>
       <c r="N84">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>484</t>
         </is>
       </c>
       <c r="C85">
-        <v>2021</v>
+        <v>1987</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>JAIR MESSIAS BOLSONARO</t>
+          <t>MIGUEL DE LA MADRID HURTADO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5593,13 +5581,13 @@
         </is>
       </c>
       <c r="F85" s="2">
-        <v>43466</v>
+        <v>30286</v>
       </c>
       <c r="G85" s="2">
-        <v>44926</v>
+        <v>32477</v>
       </c>
       <c r="H85">
-        <v>3.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -5613,12 +5601,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>PARTIDO LIBERAL</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -5627,26 +5615,26 @@
         </is>
       </c>
       <c r="N85">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>484</t>
         </is>
       </c>
       <c r="C86">
-        <v>2022</v>
+        <v>1988</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>JAIR MESSIAS BOLSONARO</t>
+          <t>CARLOS SALINAS DE GORTARI</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5655,13 +5643,13 @@
         </is>
       </c>
       <c r="F86" s="2">
-        <v>43466</v>
+        <v>32478</v>
       </c>
       <c r="G86" s="2">
-        <v>44926</v>
+        <v>34668</v>
       </c>
       <c r="H86">
-        <v>3.997260273972603</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5675,12 +5663,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>PARTIDO LIBERAL</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -5689,26 +5677,26 @@
         </is>
       </c>
       <c r="N86">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>484</t>
         </is>
       </c>
       <c r="C87">
-        <v>2023</v>
+        <v>1989</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LUIZ INÁCIO LULA DA SILVA</t>
+          <t>CARLOS SALINAS DE GORTARI</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5717,7 +5705,13 @@
         </is>
       </c>
       <c r="F87" s="2">
-        <v>44927</v>
+        <v>32478</v>
+      </c>
+      <c r="G87" s="2">
+        <v>34668</v>
+      </c>
+      <c r="H87">
+        <v>5.997260273972603</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5731,12 +5725,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>PARTIDO DE LOS TRABAJADORES</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -5745,26 +5739,26 @@
         </is>
       </c>
       <c r="N87">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>484</t>
         </is>
       </c>
       <c r="C88">
-        <v>2024</v>
+        <v>1990</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LUIZ INÁCIO LULA DA SILVA</t>
+          <t>CARLOS SALINAS DE GORTARI</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5773,7 +5767,13 @@
         </is>
       </c>
       <c r="F88" s="2">
-        <v>44927</v>
+        <v>32478</v>
+      </c>
+      <c r="G88" s="2">
+        <v>34668</v>
+      </c>
+      <c r="H88">
+        <v>5.997260273972603</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5787,12 +5787,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>PARTIDO DE LOS TRABAJADORES</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="N88">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -5816,11 +5816,11 @@
         </is>
       </c>
       <c r="C89">
-        <v>1985</v>
+        <v>1991</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>MIGUEL DE LA MADRID HURTADO</t>
+          <t>CARLOS SALINAS DE GORTARI</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="F89" s="2">
-        <v>30286</v>
+        <v>32478</v>
       </c>
       <c r="G89" s="2">
-        <v>32477</v>
+        <v>34668</v>
       </c>
       <c r="H89">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -5878,11 +5878,11 @@
         </is>
       </c>
       <c r="C90">
-        <v>1986</v>
+        <v>1992</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MIGUEL DE LA MADRID HURTADO</t>
+          <t>CARLOS SALINAS DE GORTARI</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5891,13 +5891,13 @@
         </is>
       </c>
       <c r="F90" s="2">
-        <v>30286</v>
+        <v>32478</v>
       </c>
       <c r="G90" s="2">
-        <v>32477</v>
+        <v>34668</v>
       </c>
       <c r="H90">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -5940,11 +5940,11 @@
         </is>
       </c>
       <c r="C91">
-        <v>1987</v>
+        <v>1993</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MIGUEL DE LA MADRID HURTADO</t>
+          <t>CARLOS SALINAS DE GORTARI</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5953,13 +5953,13 @@
         </is>
       </c>
       <c r="F91" s="2">
-        <v>30286</v>
+        <v>32478</v>
       </c>
       <c r="G91" s="2">
-        <v>32477</v>
+        <v>34668</v>
       </c>
       <c r="H91">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -6002,11 +6002,11 @@
         </is>
       </c>
       <c r="C92">
-        <v>1988</v>
+        <v>1994</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CARLOS SALINAS DE GORTARI</t>
+          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6015,13 +6015,13 @@
         </is>
       </c>
       <c r="F92" s="2">
-        <v>32478</v>
+        <v>34669</v>
       </c>
       <c r="G92" s="2">
-        <v>34668</v>
+        <v>36860</v>
       </c>
       <c r="H92">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="N92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -6064,11 +6064,11 @@
         </is>
       </c>
       <c r="C93">
-        <v>1989</v>
+        <v>1995</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>CARLOS SALINAS DE GORTARI</t>
+          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6077,13 +6077,13 @@
         </is>
       </c>
       <c r="F93" s="2">
-        <v>32478</v>
+        <v>34669</v>
       </c>
       <c r="G93" s="2">
-        <v>34668</v>
+        <v>36860</v>
       </c>
       <c r="H93">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -6126,11 +6126,11 @@
         </is>
       </c>
       <c r="C94">
-        <v>1990</v>
+        <v>1996</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>CARLOS SALINAS DE GORTARI</t>
+          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="F94" s="2">
-        <v>32478</v>
+        <v>34669</v>
       </c>
       <c r="G94" s="2">
-        <v>34668</v>
+        <v>36860</v>
       </c>
       <c r="H94">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="N94">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -6188,11 +6188,11 @@
         </is>
       </c>
       <c r="C95">
-        <v>1991</v>
+        <v>1997</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CARLOS SALINAS DE GORTARI</t>
+          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6201,13 +6201,13 @@
         </is>
       </c>
       <c r="F95" s="2">
-        <v>32478</v>
+        <v>34669</v>
       </c>
       <c r="G95" s="2">
-        <v>34668</v>
+        <v>36860</v>
       </c>
       <c r="H95">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="N95">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -6250,11 +6250,11 @@
         </is>
       </c>
       <c r="C96">
-        <v>1992</v>
+        <v>1998</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CARLOS SALINAS DE GORTARI</t>
+          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6263,13 +6263,13 @@
         </is>
       </c>
       <c r="F96" s="2">
-        <v>32478</v>
+        <v>34669</v>
       </c>
       <c r="G96" s="2">
-        <v>34668</v>
+        <v>36860</v>
       </c>
       <c r="H96">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="N96">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
@@ -6312,11 +6312,11 @@
         </is>
       </c>
       <c r="C97">
-        <v>1993</v>
+        <v>1999</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CARLOS SALINAS DE GORTARI</t>
+          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6325,13 +6325,13 @@
         </is>
       </c>
       <c r="F97" s="2">
-        <v>32478</v>
+        <v>34669</v>
       </c>
       <c r="G97" s="2">
-        <v>34668</v>
+        <v>36860</v>
       </c>
       <c r="H97">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -6374,11 +6374,11 @@
         </is>
       </c>
       <c r="C98">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
+          <t>VICENTE FOX QUESADA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6387,13 +6387,13 @@
         </is>
       </c>
       <c r="F98" s="2">
-        <v>34669</v>
+        <v>36861</v>
       </c>
       <c r="G98" s="2">
-        <v>36860</v>
+        <v>39051</v>
       </c>
       <c r="H98">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6407,12 +6407,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>PARTIDO ACCIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6421,7 +6421,7 @@
         </is>
       </c>
       <c r="N98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -6436,11 +6436,11 @@
         </is>
       </c>
       <c r="C99">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
+          <t>VICENTE FOX QUESADA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="F99" s="2">
-        <v>34669</v>
+        <v>36861</v>
       </c>
       <c r="G99" s="2">
-        <v>36860</v>
+        <v>39051</v>
       </c>
       <c r="H99">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>PARTIDO ACCIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -6483,7 +6483,7 @@
         </is>
       </c>
       <c r="N99">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -6498,11 +6498,11 @@
         </is>
       </c>
       <c r="C100">
-        <v>1996</v>
+        <v>2002</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
+          <t>VICENTE FOX QUESADA</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6511,13 +6511,13 @@
         </is>
       </c>
       <c r="F100" s="2">
-        <v>34669</v>
+        <v>36861</v>
       </c>
       <c r="G100" s="2">
-        <v>36860</v>
+        <v>39051</v>
       </c>
       <c r="H100">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6531,12 +6531,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>PARTIDO ACCIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="N100">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
@@ -6560,11 +6560,11 @@
         </is>
       </c>
       <c r="C101">
-        <v>1997</v>
+        <v>2003</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
+          <t>VICENTE FOX QUESADA</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="F101" s="2">
-        <v>34669</v>
+        <v>36861</v>
       </c>
       <c r="G101" s="2">
-        <v>36860</v>
+        <v>39051</v>
       </c>
       <c r="H101">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6593,12 +6593,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>PARTIDO ACCIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="N101">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -6622,11 +6622,11 @@
         </is>
       </c>
       <c r="C102">
-        <v>1998</v>
+        <v>2004</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
+          <t>VICENTE FOX QUESADA</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6635,13 +6635,13 @@
         </is>
       </c>
       <c r="F102" s="2">
-        <v>34669</v>
+        <v>36861</v>
       </c>
       <c r="G102" s="2">
-        <v>36860</v>
+        <v>39051</v>
       </c>
       <c r="H102">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>PARTIDO ACCIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="N102">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
@@ -6684,11 +6684,11 @@
         </is>
       </c>
       <c r="C103">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ERNESTO ZEDILLO PONCE DE LEÓN</t>
+          <t>VICENTE FOX QUESADA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6697,13 +6697,13 @@
         </is>
       </c>
       <c r="F103" s="2">
-        <v>34669</v>
+        <v>36861</v>
       </c>
       <c r="G103" s="2">
-        <v>36860</v>
+        <v>39051</v>
       </c>
       <c r="H103">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6717,12 +6717,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>PARTIDO ACCIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="N103">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
@@ -6746,11 +6746,11 @@
         </is>
       </c>
       <c r="C104">
-        <v>2000</v>
+        <v>2006</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VICENTE FOX QUESADA</t>
+          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6759,13 +6759,13 @@
         </is>
       </c>
       <c r="F104" s="2">
-        <v>36861</v>
+        <v>39052</v>
       </c>
       <c r="G104" s="2">
-        <v>39051</v>
+        <v>41243</v>
       </c>
       <c r="H104">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="N104">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -6808,11 +6808,11 @@
         </is>
       </c>
       <c r="C105">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VICENTE FOX QUESADA</t>
+          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6821,13 +6821,13 @@
         </is>
       </c>
       <c r="F105" s="2">
-        <v>36861</v>
+        <v>39052</v>
       </c>
       <c r="G105" s="2">
-        <v>39051</v>
+        <v>41243</v>
       </c>
       <c r="H105">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -6870,11 +6870,11 @@
         </is>
       </c>
       <c r="C106">
-        <v>2002</v>
+        <v>2008</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VICENTE FOX QUESADA</t>
+          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,13 +6883,13 @@
         </is>
       </c>
       <c r="F106" s="2">
-        <v>36861</v>
+        <v>39052</v>
       </c>
       <c r="G106" s="2">
-        <v>39051</v>
+        <v>41243</v>
       </c>
       <c r="H106">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -6932,11 +6932,11 @@
         </is>
       </c>
       <c r="C107">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VICENTE FOX QUESADA</t>
+          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6945,13 +6945,13 @@
         </is>
       </c>
       <c r="F107" s="2">
-        <v>36861</v>
+        <v>39052</v>
       </c>
       <c r="G107" s="2">
-        <v>39051</v>
+        <v>41243</v>
       </c>
       <c r="H107">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         </is>
       </c>
       <c r="N107">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -6994,11 +6994,11 @@
         </is>
       </c>
       <c r="C108">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VICENTE FOX QUESADA</t>
+          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7007,13 +7007,13 @@
         </is>
       </c>
       <c r="F108" s="2">
-        <v>36861</v>
+        <v>39052</v>
       </c>
       <c r="G108" s="2">
-        <v>39051</v>
+        <v>41243</v>
       </c>
       <c r="H108">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="N108">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
@@ -7056,11 +7056,11 @@
         </is>
       </c>
       <c r="C109">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VICENTE FOX QUESADA</t>
+          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7069,13 +7069,13 @@
         </is>
       </c>
       <c r="F109" s="2">
-        <v>36861</v>
+        <v>39052</v>
       </c>
       <c r="G109" s="2">
-        <v>39051</v>
+        <v>41243</v>
       </c>
       <c r="H109">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         </is>
       </c>
       <c r="N109">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
@@ -7118,11 +7118,11 @@
         </is>
       </c>
       <c r="C110">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
+          <t>ENRIQUE PEÑA NIETO</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7131,13 +7131,13 @@
         </is>
       </c>
       <c r="F110" s="2">
-        <v>39052</v>
+        <v>41244</v>
       </c>
       <c r="G110" s="2">
-        <v>41243</v>
+        <v>43434</v>
       </c>
       <c r="H110">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -7151,12 +7151,12 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>PARTIDO ACCIÓN NACIONAL</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="N110">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -7180,11 +7180,11 @@
         </is>
       </c>
       <c r="C111">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
+          <t>ENRIQUE PEÑA NIETO</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7193,13 +7193,13 @@
         </is>
       </c>
       <c r="F111" s="2">
-        <v>39052</v>
+        <v>41244</v>
       </c>
       <c r="G111" s="2">
-        <v>41243</v>
+        <v>43434</v>
       </c>
       <c r="H111">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -7213,12 +7213,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>PARTIDO ACCIÓN NACIONAL</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -7227,7 +7227,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -7242,11 +7242,11 @@
         </is>
       </c>
       <c r="C112">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
+          <t>ENRIQUE PEÑA NIETO</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7255,13 +7255,13 @@
         </is>
       </c>
       <c r="F112" s="2">
-        <v>39052</v>
+        <v>41244</v>
       </c>
       <c r="G112" s="2">
-        <v>41243</v>
+        <v>43434</v>
       </c>
       <c r="H112">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -7275,12 +7275,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>PARTIDO ACCIÓN NACIONAL</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -7289,7 +7289,7 @@
         </is>
       </c>
       <c r="N112">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -7304,11 +7304,11 @@
         </is>
       </c>
       <c r="C113">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
+          <t>ENRIQUE PEÑA NIETO</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7317,13 +7317,13 @@
         </is>
       </c>
       <c r="F113" s="2">
-        <v>39052</v>
+        <v>41244</v>
       </c>
       <c r="G113" s="2">
-        <v>41243</v>
+        <v>43434</v>
       </c>
       <c r="H113">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -7337,12 +7337,12 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>PARTIDO ACCIÓN NACIONAL</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="N113">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -7366,11 +7366,11 @@
         </is>
       </c>
       <c r="C114">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
+          <t>ENRIQUE PEÑA NIETO</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7379,13 +7379,13 @@
         </is>
       </c>
       <c r="F114" s="2">
-        <v>39052</v>
+        <v>41244</v>
       </c>
       <c r="G114" s="2">
-        <v>41243</v>
+        <v>43434</v>
       </c>
       <c r="H114">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -7399,12 +7399,12 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>PARTIDO ACCIÓN NACIONAL</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -7428,11 +7428,11 @@
         </is>
       </c>
       <c r="C115">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>FELIPE DE JESÚS CALDERÓN HINOJOSA</t>
+          <t>ENRIQUE PEÑA NIETO</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7441,13 +7441,13 @@
         </is>
       </c>
       <c r="F115" s="2">
-        <v>39052</v>
+        <v>41244</v>
       </c>
       <c r="G115" s="2">
-        <v>41243</v>
+        <v>43434</v>
       </c>
       <c r="H115">
-        <v>5.997267759562842</v>
+        <v>5.997260273972603</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>PARTIDO ACCIÓN NACIONAL</t>
+          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
@@ -7490,11 +7490,11 @@
         </is>
       </c>
       <c r="C116">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ENRIQUE PEÑA NIETO</t>
+          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7503,13 +7503,13 @@
         </is>
       </c>
       <c r="F116" s="2">
-        <v>41244</v>
+        <v>43435</v>
       </c>
       <c r="G116" s="2">
-        <v>43434</v>
+        <v>45626</v>
       </c>
       <c r="H116">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -7523,12 +7523,12 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="N116">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -7552,11 +7552,11 @@
         </is>
       </c>
       <c r="C117">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ENRIQUE PEÑA NIETO</t>
+          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7565,13 +7565,13 @@
         </is>
       </c>
       <c r="F117" s="2">
-        <v>41244</v>
+        <v>43435</v>
       </c>
       <c r="G117" s="2">
-        <v>43434</v>
+        <v>45626</v>
       </c>
       <c r="H117">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="N117">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -7614,11 +7614,11 @@
         </is>
       </c>
       <c r="C118">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ENRIQUE PEÑA NIETO</t>
+          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7627,13 +7627,13 @@
         </is>
       </c>
       <c r="F118" s="2">
-        <v>41244</v>
+        <v>43435</v>
       </c>
       <c r="G118" s="2">
-        <v>43434</v>
+        <v>45626</v>
       </c>
       <c r="H118">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7647,12 +7647,12 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -7661,7 +7661,7 @@
         </is>
       </c>
       <c r="N118">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -7676,11 +7676,11 @@
         </is>
       </c>
       <c r="C119">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ENRIQUE PEÑA NIETO</t>
+          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7689,13 +7689,13 @@
         </is>
       </c>
       <c r="F119" s="2">
-        <v>41244</v>
+        <v>43435</v>
       </c>
       <c r="G119" s="2">
-        <v>43434</v>
+        <v>45626</v>
       </c>
       <c r="H119">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -7709,12 +7709,12 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="N119">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -7738,11 +7738,11 @@
         </is>
       </c>
       <c r="C120">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ENRIQUE PEÑA NIETO</t>
+          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7751,13 +7751,13 @@
         </is>
       </c>
       <c r="F120" s="2">
-        <v>41244</v>
+        <v>43435</v>
       </c>
       <c r="G120" s="2">
-        <v>43434</v>
+        <v>45626</v>
       </c>
       <c r="H120">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -7771,12 +7771,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="N120">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
@@ -7800,11 +7800,11 @@
         </is>
       </c>
       <c r="C121">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ENRIQUE PEÑA NIETO</t>
+          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7813,13 +7813,13 @@
         </is>
       </c>
       <c r="F121" s="2">
-        <v>41244</v>
+        <v>43435</v>
       </c>
       <c r="G121" s="2">
-        <v>43434</v>
+        <v>45626</v>
       </c>
       <c r="H121">
-        <v>5.997260273972603</v>
+        <v>5.997267759562842</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>PARTIDO REVOLUCIONARIO INSTITUCIONAL</t>
+          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="N121">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
@@ -7862,26 +7862,20 @@
         </is>
       </c>
       <c r="C122">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
+          <t>CLAUDIA SHEINBAUM PARDO</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F122" s="2">
-        <v>43435</v>
-      </c>
-      <c r="G122" s="2">
-        <v>45626</v>
-      </c>
-      <c r="H122">
-        <v>5.997267759562842</v>
+        <v>45627</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -7909,373 +7903,7 @@
         </is>
       </c>
       <c r="N122">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>MEXICO</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="C123">
-        <v>2019</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F123" s="2">
-        <v>43435</v>
-      </c>
-      <c r="G123" s="2">
-        <v>45626</v>
-      </c>
-      <c r="H123">
-        <v>5.997267759562842</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N123">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>MEXICO</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="C124">
-        <v>2020</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F124" s="2">
-        <v>43435</v>
-      </c>
-      <c r="G124" s="2">
-        <v>45626</v>
-      </c>
-      <c r="H124">
-        <v>5.997267759562842</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N124">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>MEXICO</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="C125">
-        <v>2021</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F125" s="2">
-        <v>43435</v>
-      </c>
-      <c r="G125" s="2">
-        <v>45626</v>
-      </c>
-      <c r="H125">
-        <v>5.997267759562842</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N125">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>MEXICO</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="C126">
-        <v>2022</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F126" s="2">
-        <v>43435</v>
-      </c>
-      <c r="G126" s="2">
-        <v>45626</v>
-      </c>
-      <c r="H126">
-        <v>5.997267759562842</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N126">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>MEXICO</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="C127">
-        <v>2023</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>ANDRÉS MANUEL LÓPEZ OBRADOR</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F127" s="2">
-        <v>43435</v>
-      </c>
-      <c r="G127" s="2">
-        <v>45626</v>
-      </c>
-      <c r="H127">
-        <v>5.997267759562842</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N127">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>MEXICO</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="C128">
-        <v>2024</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>CLAUDIA SHEINBAUM PARDO</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F128" s="2">
-        <v>45627</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>MOVIMIENTO DE REGENERACIÓN NACIONAL</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N128">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
